--- a/QLNS/FileExcels/BC_MangLuoiLD_09_TCCB.xlsx
+++ b/QLNS/FileExcels/BC_MangLuoiLD_09_TCCB.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VBSP_DEV\AZUREDEPOPS_PROJECT\VBSP-QLNS\VBSP-QLNS\QLNS\FileExcels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="6468" tabRatio="695"/>
   </bookViews>
@@ -111,12 +116,6 @@
  tổng số cán bộ tín dụng</t>
   </si>
   <si>
-    <t>Tổng số xã, phường, thị trấn</t>
-  </si>
-  <si>
-    <t>Số khách hàng còn dư nợ</t>
-  </si>
-  <si>
     <t>Tổng 
 dư nợ
 (tỷ đồng)</t>
@@ -143,6 +142,12 @@
       </rPr>
       <t>.................</t>
     </r>
+  </si>
+  <si>
+    <t>Tổng số xã, phường, đặc khu</t>
+  </si>
+  <si>
+    <t>Số khách hàng dư nợ</t>
   </si>
 </sst>
 </file>
@@ -396,44 +401,44 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -496,7 +501,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -531,7 +536,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -760,94 +765,94 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
     </row>
     <row r="3" spans="1:10" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
       <c r="F3" s="3"/>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
     </row>
     <row r="4" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
     </row>
     <row r="6" spans="1:10" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="27" t="s">
+      <c r="B7" s="26"/>
+      <c r="C7" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="31"/>
+      <c r="F7" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="21"/>
     </row>
-    <row r="8" spans="1:10" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
+    <row r="8" spans="1:10" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
       <c r="F8" s="7" t="s">
         <v>28</v>
       </c>
@@ -855,13 +860,13 @@
         <v>29</v>
       </c>
       <c r="H8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="10" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -875,7 +880,7 @@
         <v>13</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>14</v>
@@ -887,7 +892,7 @@
         <v>16</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>17</v>
@@ -916,7 +921,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>9</v>
@@ -934,16 +939,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="G2:J2"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="A7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.65" right="0.55000000000000004" top="0.65" bottom="0.55000000000000004" header="0.05" footer="0.05"/>
